--- a/erp-server/erp-server-file/src/main/resources/excel/plm/cfgMoldReturn.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/plm/cfgMoldReturn.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>模具编码</t>
   </si>
@@ -38,33 +38,36 @@
     <t>策略状态</t>
   </si>
   <si>
-    <t>返还标准</t>
+    <t>预警标准</t>
   </si>
   <si>
     <t>供应商</t>
   </si>
   <si>
+    <t>寿命数量</t>
+  </si>
+  <si>
+    <t>预警寿命（数量）</t>
+  </si>
+  <si>
+    <t>预警寿命（%）</t>
+  </si>
+  <si>
+    <t>开始日期</t>
+  </si>
+  <si>
+    <t>结束日期</t>
+  </si>
+  <si>
+    <t>最新修改人</t>
+  </si>
+  <si>
+    <t>最新修改时间</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
-    <t>返还数量上限</t>
-  </si>
-  <si>
-    <t>返还金额</t>
-  </si>
-  <si>
-    <t>开始日期</t>
-  </si>
-  <si>
-    <t>结束日期</t>
-  </si>
-  <si>
-    <t>最新修改人</t>
-  </si>
-  <si>
-    <t>最新修改时间</t>
-  </si>
-  <si>
     <t>{.moldCode}</t>
   </si>
   <si>
@@ -80,25 +83,28 @@
     <t>{.supplierName}</t>
   </si>
   <si>
+    <t>{.lifeQty}</t>
+  </si>
+  <si>
+    <t>{.alertLifeQty}</t>
+  </si>
+  <si>
+    <t>{.alertLifeRate}</t>
+  </si>
+  <si>
+    <t>{.startDate}</t>
+  </si>
+  <si>
+    <t>{.endDate}</t>
+  </si>
+  <si>
+    <t>{.updateUserName}</t>
+  </si>
+  <si>
+    <t>{.updateTime}</t>
+  </si>
+  <si>
     <t>{.remark}</t>
-  </si>
-  <si>
-    <t>{.returnQtyLimit}</t>
-  </si>
-  <si>
-    <t>{.returnPrice}</t>
-  </si>
-  <si>
-    <t>{.startDate}</t>
-  </si>
-  <si>
-    <t>{.endDate}</t>
-  </si>
-  <si>
-    <t>{.updateUserName}</t>
-  </si>
-  <si>
-    <t>{.updateTime}</t>
   </si>
 </sst>
 </file>
@@ -111,7 +117,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -123,6 +129,17 @@
       <sz val="9.75"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -590,144 +607,147 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1041,11 +1061,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="18.625" customWidth="1"/>
-    <col min="2" max="2" width="28.125" customWidth="1"/>
+    <col min="2" max="2" width="19.625" customWidth="1"/>
     <col min="3" max="3" width="19.25" customWidth="1"/>
     <col min="4" max="4" width="16.75" customWidth="1"/>
     <col min="5" max="5" width="18.625" customWidth="1"/>
@@ -1060,80 +1080,86 @@
     <col min="14" max="14" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" customFormat="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" customFormat="1" spans="1:13">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L2" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="M2" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/plm/cfgMoldReturn.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/plm/cfgMoldReturn.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>模具编码</t>
   </si>
@@ -65,6 +65,9 @@
     <t>最新修改时间</t>
   </si>
   <si>
+    <t>通知类型</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
@@ -102,6 +105,9 @@
   </si>
   <si>
     <t>{.updateTime}</t>
+  </si>
+  <si>
+    <t>{.noticeTypeName}</t>
   </si>
   <si>
     <t>{.remark}</t>
@@ -1061,7 +1067,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="18.625" customWidth="1"/>
@@ -1076,11 +1082,11 @@
     <col min="10" max="10" width="20" customWidth="1"/>
     <col min="11" max="11" width="24.125" customWidth="1"/>
     <col min="12" max="12" width="15.25" customWidth="1"/>
-    <col min="13" max="13" width="15" customWidth="1"/>
-    <col min="14" max="14" width="18.125" customWidth="1"/>
+    <col min="13" max="14" width="15" customWidth="1"/>
+    <col min="15" max="15" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:13">
+    <row r="1" customFormat="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1117,49 +1123,55 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" customFormat="1" spans="1:13">
+    <row r="2" customFormat="1" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M2" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/plm/cfgMoldReturn.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/plm/cfgMoldReturn.xlsx
@@ -38,39 +38,39 @@
     <t>策略状态</t>
   </si>
   <si>
-    <t>预警标准</t>
+    <t>返还标准</t>
   </si>
   <si>
     <t>供应商</t>
   </si>
   <si>
-    <t>寿命数量</t>
-  </si>
-  <si>
-    <t>预警寿命（数量）</t>
-  </si>
-  <si>
-    <t>预警寿命（%）</t>
-  </si>
-  <si>
     <t>开始日期</t>
   </si>
   <si>
     <t>结束日期</t>
   </si>
   <si>
+    <t>通知类型</t>
+  </si>
+  <si>
     <t>最新修改人</t>
   </si>
   <si>
     <t>最新修改时间</t>
   </si>
   <si>
-    <t>通知类型</t>
-  </si>
-  <si>
     <t>备注</t>
   </si>
   <si>
+    <t>返还数量限制</t>
+  </si>
+  <si>
+    <t>归还价格</t>
+  </si>
+  <si>
+    <t>明细备注备注</t>
+  </si>
+  <si>
     <t>{.moldCode}</t>
   </si>
   <si>
@@ -86,31 +86,31 @@
     <t>{.supplierName}</t>
   </si>
   <si>
-    <t>{.lifeQty}</t>
-  </si>
-  <si>
-    <t>{.alertLifeQty}</t>
-  </si>
-  <si>
-    <t>{.alertLifeRate}</t>
-  </si>
-  <si>
     <t>{.startDate}</t>
   </si>
   <si>
     <t>{.endDate}</t>
   </si>
   <si>
+    <t>{.noticeTypeName}</t>
+  </si>
+  <si>
     <t>{.updateUserName}</t>
   </si>
   <si>
     <t>{.updateTime}</t>
   </si>
   <si>
-    <t>{.noticeTypeName}</t>
-  </si>
-  <si>
     <t>{.remark}</t>
+  </si>
+  <si>
+    <t>{.returnQtyLimit}</t>
+  </si>
+  <si>
+    <t>{.returnPrice}</t>
+  </si>
+  <si>
+    <t>{.detailRemark}</t>
   </si>
 </sst>
 </file>
@@ -123,7 +123,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -140,11 +140,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF333333"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -613,137 +608,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -751,9 +746,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1075,15 +1067,13 @@
     <col min="3" max="3" width="19.25" customWidth="1"/>
     <col min="4" max="4" width="16.75" customWidth="1"/>
     <col min="5" max="5" width="18.625" customWidth="1"/>
-    <col min="6" max="6" width="17.875" customWidth="1"/>
+    <col min="6" max="6" width="20.125" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="17.875" customWidth="1"/>
-    <col min="9" max="9" width="20.125" customWidth="1"/>
-    <col min="10" max="10" width="20" customWidth="1"/>
-    <col min="11" max="11" width="24.125" customWidth="1"/>
-    <col min="12" max="12" width="15.25" customWidth="1"/>
-    <col min="13" max="14" width="15" customWidth="1"/>
-    <col min="15" max="15" width="18.125" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="24.125" customWidth="1"/>
+    <col min="10" max="10" width="15.25" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="13" max="13" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" spans="1:14">
@@ -1102,13 +1092,13 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -1123,7 +1113,7 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
